--- a/data/trans_orig/P21D_2_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P21D_2_R-Habitat-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, necesitando atención sanitaria dental, no la pudo recibir por motivos económicos en 2023</t>
+          <t>Población que, necesitando atención sanitaria dental, no la pudo recibir por motivos económicos en 2023 (tasa de respuesta: 99,84%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3315</t>
+          <t>3291</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12545</t>
+          <t>12436</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4502</t>
+          <t>4520</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>15545</t>
+          <t>14286</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>9362</t>
+          <t>9744</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>23133</t>
+          <t>23256</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,11%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>254054</t>
+          <t>254163</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>263284</t>
+          <t>263308</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,29%</t>
+          <t>95,34%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>283584</t>
+          <t>284843</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>294627</t>
+          <t>294609</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,8%</t>
+          <t>95,22%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>542594</t>
+          <t>542471</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>556365</t>
+          <t>555983</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>95,89%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,28%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>840</t>
+          <t>629</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13260</t>
+          <t>13910</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3314</t>
+          <t>3340</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11238</t>
+          <t>11038</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5145</t>
+          <t>4936</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>20896</t>
+          <t>20410</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,85%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>645129</t>
+          <t>644479</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>657549</t>
+          <t>657760</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,87%</t>
+          <t>99,9%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>436117</t>
+          <t>436317</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>444041</t>
+          <t>444015</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>97,53%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1084848</t>
+          <t>1085334</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1100599</t>
+          <t>1100808</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,55%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5270</t>
+          <t>5567</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17753</t>
+          <t>18128</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2235</t>
+          <t>2230</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12121</t>
+          <t>13311</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9192</t>
+          <t>8917</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>24075</t>
+          <t>24249</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,67%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>313085</t>
+          <t>312710</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>325568</t>
+          <t>325271</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,63%</t>
+          <t>94,52%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>317269</t>
+          <t>316079</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>327155</t>
+          <t>327160</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,7 +1579,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>95,96%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>636152</t>
+          <t>635978</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>651035</t>
+          <t>651310</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>96,33%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,65%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>836</t>
+          <t>941</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8020</t>
+          <t>7780</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8171</t>
+          <t>8083</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>39711</t>
+          <t>36574</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>11439</t>
+          <t>11096</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>41945</t>
+          <t>44069</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,77%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>399933</t>
+          <t>400173</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>407117</t>
+          <t>407012</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,8%</t>
+          <t>99,77%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>476572</t>
+          <t>479709</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>508112</t>
+          <t>508200</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,31%</t>
+          <t>92,92%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>882290</t>
+          <t>880166</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>912796</t>
+          <t>913139</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,23%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,8%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>15063</t>
+          <t>14538</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>37634</t>
+          <t>37524</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,7 +2117,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>25945</t>
+          <t>26281</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>56964</t>
+          <t>59403</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>45105</t>
+          <t>44458</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>82350</t>
+          <t>84305</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,59%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1626144</t>
+          <t>1626254</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1648715</t>
+          <t>1649240</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2235,7 +2235,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,13%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1535192</t>
+          <t>1532753</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1566211</t>
+          <t>1565875</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>96,27%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3173584</t>
+          <t>3171629</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3210829</t>
+          <t>3211476</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,63%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P21D_2_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P21D_2_R-Habitat-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>6844</t>
+          <t>9219</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3291</t>
+          <t>4952</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12436</t>
+          <t>16101</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>8441</t>
+          <t>8640</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4520</t>
+          <t>4392</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14286</t>
+          <t>14698</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>15286</t>
+          <t>17859</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>9744</t>
+          <t>11540</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>23256</t>
+          <t>25048</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,1%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>259755</t>
+          <t>278904</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>254163</t>
+          <t>272022</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>263308</t>
+          <t>283171</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>94,41%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>290688</t>
+          <t>314869</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>284843</t>
+          <t>308811</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>294609</t>
+          <t>319117</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>97,33%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>95,46%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>550441</t>
+          <t>593773</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>542471</t>
+          <t>586584</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>555983</t>
+          <t>600092</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,08%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>95,9%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,11%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>266599</t>
+          <t>288123</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>266599</t>
+          <t>288123</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>266599</t>
+          <t>288123</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>299129</t>
+          <t>323509</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>299129</t>
+          <t>323509</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>299129</t>
+          <t>323509</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>565727</t>
+          <t>611632</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>565727</t>
+          <t>611632</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>565727</t>
+          <t>611632</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5391</t>
+          <t>4925</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>629</t>
+          <t>1637</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13910</t>
+          <t>11123</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6375</t>
+          <t>10474</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3340</t>
+          <t>5320</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11038</t>
+          <t>19143</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>11766</t>
+          <t>15399</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4936</t>
+          <t>9455</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>20410</t>
+          <t>26219</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>2,69%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>652998</t>
+          <t>465283</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>644479</t>
+          <t>459085</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>657760</t>
+          <t>468571</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,9%</t>
+          <t>99,65%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>440980</t>
+          <t>492920</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>436317</t>
+          <t>484251</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>444015</t>
+          <t>498074</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>96,2%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>98,94%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1093978</t>
+          <t>958202</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1085334</t>
+          <t>947382</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1100808</t>
+          <t>964146</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,42%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,03%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>658389</t>
+          <t>470208</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>658389</t>
+          <t>470208</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>658389</t>
+          <t>470208</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>447355</t>
+          <t>503394</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>447355</t>
+          <t>503394</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>447355</t>
+          <t>503394</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1105744</t>
+          <t>973601</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1105744</t>
+          <t>973601</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1105744</t>
+          <t>973601</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>10181</t>
+          <t>15640</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5567</t>
+          <t>8666</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>18128</t>
+          <t>26004</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>4929</t>
+          <t>9239</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2230</t>
+          <t>4848</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13311</t>
+          <t>16287</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>15110</t>
+          <t>24879</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8917</t>
+          <t>16019</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>24249</t>
+          <t>36359</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>4,81%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>320657</t>
+          <t>360944</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>312710</t>
+          <t>350580</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>325271</t>
+          <t>367918</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>93,09%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>324461</t>
+          <t>369410</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>316079</t>
+          <t>362362</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>327160</t>
+          <t>373801</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>97,56%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>95,7%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>645117</t>
+          <t>730353</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>635978</t>
+          <t>718873</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>651310</t>
+          <t>739213</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>96,71%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>95,19%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>97,88%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>330838</t>
+          <t>376584</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>330838</t>
+          <t>376584</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>330838</t>
+          <t>376584</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>329390</t>
+          <t>378649</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>329390</t>
+          <t>378649</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>329390</t>
+          <t>378649</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>660227</t>
+          <t>755232</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>660227</t>
+          <t>755232</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>660227</t>
+          <t>755232</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3071</t>
+          <t>3757</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>941</t>
+          <t>925</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7780</t>
+          <t>9558</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>16688</t>
+          <t>12201</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8083</t>
+          <t>7797</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>36574</t>
+          <t>19299</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>19759</t>
+          <t>15958</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>11096</t>
+          <t>10177</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>44069</t>
+          <t>24728</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>2,68%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>404882</t>
+          <t>429602</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>400173</t>
+          <t>423801</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>407012</t>
+          <t>432434</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,13%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>97,79%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,77%</t>
+          <t>99,79%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>499595</t>
+          <t>476859</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>479709</t>
+          <t>469761</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>508200</t>
+          <t>481263</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,92%</t>
+          <t>96,05%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,41%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>904476</t>
+          <t>906461</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>880166</t>
+          <t>897691</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>913139</t>
+          <t>912242</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>97,32%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,9%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>407953</t>
+          <t>433359</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>407953</t>
+          <t>433359</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>407953</t>
+          <t>433359</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>516283</t>
+          <t>489060</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>516283</t>
+          <t>489060</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>516283</t>
+          <t>489060</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>924235</t>
+          <t>922419</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>924235</t>
+          <t>922419</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>924235</t>
+          <t>922419</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,32 +2097,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>25487</t>
+          <t>33541</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>14538</t>
+          <t>24192</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>37524</t>
+          <t>48147</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>36433</t>
+          <t>40555</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>26281</t>
+          <t>30641</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>59403</t>
+          <t>54152</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>61921</t>
+          <t>74096</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>44458</t>
+          <t>60451</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>84305</t>
+          <t>91886</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,82%</t>
         </is>
       </c>
     </row>
@@ -2210,32 +2210,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1638291</t>
+          <t>1534733</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1626254</t>
+          <t>1520127</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1649240</t>
+          <t>1544082</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>96,93%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,32 +2245,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1555723</t>
+          <t>1654056</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1532753</t>
+          <t>1640459</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1565875</t>
+          <t>1663970</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>3194013</t>
+          <t>3188789</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3171629</t>
+          <t>3170999</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3211476</t>
+          <t>3202434</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,15%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1663778</t>
+          <t>1568274</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1663778</t>
+          <t>1568274</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1663778</t>
+          <t>1568274</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1592156</t>
+          <t>1694611</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1592156</t>
+          <t>1694611</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1592156</t>
+          <t>1694611</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>3255934</t>
+          <t>3262885</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>3255934</t>
+          <t>3262885</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>3255934</t>
+          <t>3262885</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
